--- a/saved_models/results.xlsx
+++ b/saved_models/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharmProjects\AtomEnergyLevels\saved_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004CF51B-5782-46CA-AE28-F6898666CA40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B632F2-4FB9-4E05-95FF-ADD0C227CC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6870" yWindow="2310" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="K" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>Mean Squared Error (MSE)</t>
   </si>
@@ -81,10 +81,22 @@
     <t>Binded, KDE</t>
   </si>
   <si>
-    <t>xps</t>
-  </si>
-  <si>
     <t>surface</t>
+  </si>
+  <si>
+    <t>3867.19 cm⁻¹</t>
+  </si>
+  <si>
+    <t>2154.24 cm⁻¹</t>
+  </si>
+  <si>
+    <t>1112.96 cm⁻¹</t>
+  </si>
+  <si>
+    <t>17131.57 cm⁻¹</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3867.19 cm⁻¹</t>
   </si>
 </sst>
 </file>
@@ -120,8 +132,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -403,16 +416,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>14</v>
       </c>
@@ -426,66 +439,105 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2">
+        <v>14955167</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E2">
+        <v>14955168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C6">
+        <v>0.216</v>
+      </c>
+      <c r="E6">
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="C7" s="1">
+        <v>9.6799999999999997E-2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>9.6799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/saved_models/results.xlsx
+++ b/saved_models/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharmProjects\AtomEnergyLevels\saved_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B632F2-4FB9-4E05-95FF-ADD0C227CC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9A952D-1025-4817-A2EF-C99414EE4EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6870" yWindow="2310" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="K" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>Mean Squared Error (MSE)</t>
   </si>
@@ -81,9 +81,6 @@
     <t>Binded, KDE</t>
   </si>
   <si>
-    <t>surface</t>
-  </si>
-  <si>
     <t>3867.19 cm⁻¹</t>
   </si>
   <si>
@@ -97,6 +94,9 @@
   </si>
   <si>
     <t xml:space="preserve"> 3867.19 cm⁻¹</t>
+  </si>
+  <si>
+    <t>13613092.00</t>
   </si>
 </sst>
 </file>
@@ -416,16 +416,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
         <v>14</v>
       </c>
@@ -439,7 +439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -450,13 +450,13 @@
         <v>14955167</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>14955168</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -464,13 +464,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -478,13 +481,16 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -492,13 +498,16 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -508,11 +517,14 @@
       <c r="C6">
         <v>0.216</v>
       </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
       <c r="E6">
         <v>0.216</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -522,11 +534,14 @@
       <c r="C7" s="1">
         <v>9.6799999999999997E-2</v>
       </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
       <c r="E7" s="1">
         <v>9.6799999999999997E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -534,10 +549,13 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/saved_models/results.xlsx
+++ b/saved_models/results.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharmProjects\AtomEnergyLevels\saved_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9A952D-1025-4817-A2EF-C99414EE4EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC354A9-FB50-467F-BFBE-14D82775DC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="13763" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="K" sheetId="1" r:id="rId1"/>
+    <sheet name="predictions_K" sheetId="2" r:id="rId2"/>
+    <sheet name="valence_analysis" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="69">
   <si>
     <t>Mean Squared Error (MSE)</t>
   </si>
@@ -48,27 +50,6 @@
     <t>Maximum Error</t>
   </si>
   <si>
-    <t>13613089.00</t>
-  </si>
-  <si>
-    <t>3689.59 cm⁻¹</t>
-  </si>
-  <si>
-    <t>2024.68 cm⁻¹</t>
-  </si>
-  <si>
-    <t>1238.25 cm⁻¹</t>
-  </si>
-  <si>
-    <t>0.2864</t>
-  </si>
-  <si>
-    <t>9.21%</t>
-  </si>
-  <si>
-    <t>16832.54 cm⁻¹</t>
-  </si>
-  <si>
     <t>Binded, NoWeight</t>
   </si>
   <si>
@@ -81,22 +62,178 @@
     <t>Binded, KDE</t>
   </si>
   <si>
-    <t>3867.19 cm⁻¹</t>
-  </si>
-  <si>
-    <t>2154.24 cm⁻¹</t>
-  </si>
-  <si>
-    <t>1112.96 cm⁻¹</t>
-  </si>
-  <si>
-    <t>17131.57 cm⁻¹</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 3867.19 cm⁻¹</t>
-  </si>
-  <si>
-    <t>13613092.00</t>
+    <t>Raw, no weights</t>
+  </si>
+  <si>
+    <t>Raw, Bins</t>
+  </si>
+  <si>
+    <t>Raw, Distance</t>
+  </si>
+  <si>
+    <t>Raw, KDE</t>
+  </si>
+  <si>
+    <t>True_Energy_cm-1</t>
+  </si>
+  <si>
+    <t>Predicted_Energy_cm-1</t>
+  </si>
+  <si>
+    <t>Absolute_Error_cm-1</t>
+  </si>
+  <si>
+    <t>Percentage_Error</t>
+  </si>
+  <si>
+    <t>val_e1_n</t>
+  </si>
+  <si>
+    <t>val_e1_l</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>S_qn</t>
+  </si>
+  <si>
+    <t>L_qn</t>
+  </si>
+  <si>
+    <t>Configuration</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>3p6.4p</t>
+  </si>
+  <si>
+    <t>2P*</t>
+  </si>
+  <si>
+    <t>3p6.6p</t>
+  </si>
+  <si>
+    <t>3p6.5g</t>
+  </si>
+  <si>
+    <t>2G</t>
+  </si>
+  <si>
+    <t>3p6.9p</t>
+  </si>
+  <si>
+    <t>3p6.9f</t>
+  </si>
+  <si>
+    <t>2F*</t>
+  </si>
+  <si>
+    <t>3p6.10d</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>3p6.12p</t>
+  </si>
+  <si>
+    <t>3p6.14p</t>
+  </si>
+  <si>
+    <t>3p6.13d</t>
+  </si>
+  <si>
+    <t>3p6.15d</t>
+  </si>
+  <si>
+    <t>3p6.16d</t>
+  </si>
+  <si>
+    <t>3p6.19s</t>
+  </si>
+  <si>
+    <t>2S</t>
+  </si>
+  <si>
+    <t>3p6.18d</t>
+  </si>
+  <si>
+    <t>3p6.20s</t>
+  </si>
+  <si>
+    <t>3p6.19d</t>
+  </si>
+  <si>
+    <t>3p6.22d</t>
+  </si>
+  <si>
+    <t>3p6.24d</t>
+  </si>
+  <si>
+    <t>3p6.28s</t>
+  </si>
+  <si>
+    <t>3p6.27d</t>
+  </si>
+  <si>
+    <t>3p6.38d</t>
+  </si>
+  <si>
+    <t>3p6.42s</t>
+  </si>
+  <si>
+    <t>3p6.46d</t>
+  </si>
+  <si>
+    <t>raw no weights</t>
+  </si>
+  <si>
+    <t>raw bins</t>
+  </si>
+  <si>
+    <t>raw distance</t>
+  </si>
+  <si>
+    <t>raw kde</t>
+  </si>
+  <si>
+    <t>valence electrons</t>
+  </si>
+  <si>
+    <t>raw, no weights</t>
+  </si>
+  <si>
+    <t>mse</t>
+  </si>
+  <si>
+    <t>rmse</t>
+  </si>
+  <si>
+    <t>mae</t>
+  </si>
+  <si>
+    <t>median_ae</t>
+  </si>
+  <si>
+    <t>r2</t>
+  </si>
+  <si>
+    <t>mape</t>
+  </si>
+  <si>
+    <t>max_error</t>
+  </si>
+  <si>
+    <t>number features</t>
+  </si>
+  <si>
+    <t>binded, no weights</t>
+  </si>
+  <si>
+    <t>inversed binded, no weights</t>
   </si>
 </sst>
 </file>
@@ -112,12 +249,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -132,9 +281,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,147 +567,2124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="30.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.265625" customWidth="1"/>
+    <col min="3" max="3" width="11.46484375" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
+      <c r="B2">
+        <v>13201036</v>
       </c>
       <c r="C2">
-        <v>14955167</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
+        <v>13201036</v>
+      </c>
+      <c r="D2">
+        <v>13201036</v>
       </c>
       <c r="E2">
-        <v>14955168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+        <v>13201036</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B3">
+        <v>3633.32299804687</v>
+      </c>
+      <c r="C3">
+        <v>3633.32299804687</v>
+      </c>
+      <c r="D3">
+        <v>3633.32299804687</v>
+      </c>
+      <c r="E3">
+        <v>3633.32299804687</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B4">
+        <v>2027.59313964843</v>
+      </c>
+      <c r="C4">
+        <v>2027.59313964843</v>
+      </c>
+      <c r="D4">
+        <v>2027.59313964843</v>
+      </c>
+      <c r="E4">
+        <v>2027.59326171875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B5">
+        <v>1243.9453125</v>
+      </c>
+      <c r="C5">
+        <v>1243.9453125</v>
+      </c>
+      <c r="D5">
+        <v>1243.9453125</v>
+      </c>
+      <c r="E5">
+        <v>1243.9453125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>11</v>
+      <c r="B6">
+        <v>0.30797845125198298</v>
       </c>
       <c r="C6">
-        <v>0.216</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
+        <v>0.30797845125198298</v>
+      </c>
+      <c r="D6">
+        <v>0.30797845125198298</v>
       </c>
       <c r="E6">
-        <v>0.216</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0.30797845125198298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1">
-        <v>9.6799999999999997E-2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="1">
-        <v>9.6799999999999997E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B7">
+        <v>9.1373691558837802</v>
+      </c>
+      <c r="C7">
+        <v>9.1373691558837802</v>
+      </c>
+      <c r="D7">
+        <v>9.1373691558837802</v>
+      </c>
+      <c r="E7">
+        <v>9.1373691558837802</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8">
+        <v>16457.9375</v>
+      </c>
+      <c r="C8">
+        <v>16457.9375</v>
+      </c>
+      <c r="D8">
+        <v>16457.9375</v>
+      </c>
+      <c r="E8">
+        <v>16457.9375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F66CB074-F1A7-4A32-A05D-3F96E415786B}">
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>12985.184999999999</v>
+      </c>
+      <c r="B3">
+        <v>29443.123</v>
+      </c>
+      <c r="C3">
+        <v>30814.620999999999</v>
+      </c>
+      <c r="D3">
+        <v>30448.745999999999</v>
+      </c>
+      <c r="E3">
+        <v>29520.469000000001</v>
+      </c>
+      <c r="G3">
+        <v>16457.937999999998</v>
+      </c>
+      <c r="H3">
+        <v>126.74396</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>0.5</v>
+      </c>
+      <c r="L3">
+        <v>0.5</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>29007.71</v>
+      </c>
+      <c r="B4">
+        <v>29153.208999999999</v>
+      </c>
+      <c r="C4">
+        <v>29472.673999999999</v>
+      </c>
+      <c r="D4">
+        <v>29346.363000000001</v>
+      </c>
+      <c r="E4">
+        <v>30597.138999999999</v>
+      </c>
+      <c r="G4">
+        <v>145.49805000000001</v>
+      </c>
+      <c r="H4">
+        <v>0.50158404999999995</v>
+      </c>
+      <c r="I4">
+        <v>6</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1.5</v>
+      </c>
+      <c r="L4">
+        <v>0.5</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>30617.31</v>
+      </c>
+      <c r="B5">
+        <v>33108.29</v>
+      </c>
+      <c r="C5">
+        <v>33274.637000000002</v>
+      </c>
+      <c r="D5">
+        <v>33003.137000000002</v>
+      </c>
+      <c r="E5">
+        <v>35694.934000000001</v>
+      </c>
+      <c r="G5">
+        <v>2490.9785000000002</v>
+      </c>
+      <c r="H5">
+        <v>8.1358499999999996</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>3.5</v>
+      </c>
+      <c r="L5">
+        <v>0.5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>30617.31</v>
+      </c>
+      <c r="B6">
+        <v>33670.519999999997</v>
+      </c>
+      <c r="C6">
+        <v>33459.370000000003</v>
+      </c>
+      <c r="D6">
+        <v>33280.019999999997</v>
+      </c>
+      <c r="E6">
+        <v>35942.906000000003</v>
+      </c>
+      <c r="G6">
+        <v>3053.2089999999998</v>
+      </c>
+      <c r="H6">
+        <v>9.9721650000000004</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>4.5</v>
+      </c>
+      <c r="L6">
+        <v>0.5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>32941.925999999999</v>
+      </c>
+      <c r="B7">
+        <v>30192.865000000002</v>
+      </c>
+      <c r="C7">
+        <v>30534.28</v>
+      </c>
+      <c r="D7">
+        <v>30514.865000000002</v>
+      </c>
+      <c r="E7">
+        <v>31280.616999999998</v>
+      </c>
+      <c r="G7">
+        <v>2749.0605</v>
+      </c>
+      <c r="H7">
+        <v>8.3451730000000008</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1.5</v>
+      </c>
+      <c r="L7">
+        <v>0.5</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>33652.32</v>
+      </c>
+      <c r="B8">
+        <v>33013.07</v>
+      </c>
+      <c r="C8">
+        <v>33165.004000000001</v>
+      </c>
+      <c r="D8">
+        <v>33078.296999999999</v>
+      </c>
+      <c r="E8">
+        <v>34036.9</v>
+      </c>
+      <c r="G8">
+        <v>639.25</v>
+      </c>
+      <c r="H8">
+        <v>1.8995719</v>
+      </c>
+      <c r="I8">
+        <v>9</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <v>2.5</v>
+      </c>
+      <c r="L8">
+        <v>0.5</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="N8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>33851.593999999997</v>
+      </c>
+      <c r="B9">
+        <v>32656.76</v>
+      </c>
+      <c r="C9">
+        <v>33073.434000000001</v>
+      </c>
+      <c r="D9">
+        <v>32941.605000000003</v>
+      </c>
+      <c r="E9">
+        <v>33195.593999999997</v>
+      </c>
+      <c r="G9">
+        <v>1194.8340000000001</v>
+      </c>
+      <c r="H9">
+        <v>3.5296240000000001</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>2.5</v>
+      </c>
+      <c r="L9">
+        <v>0.5</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9" t="s">
+        <v>34</v>
+      </c>
+      <c r="O9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>33972.207000000002</v>
+      </c>
+      <c r="B10">
+        <v>32856.726999999999</v>
+      </c>
+      <c r="C10">
+        <v>33381.22</v>
+      </c>
+      <c r="D10">
+        <v>33447.714999999997</v>
+      </c>
+      <c r="E10">
+        <v>30926.044999999998</v>
+      </c>
+      <c r="G10">
+        <v>1115.4804999999999</v>
+      </c>
+      <c r="H10">
+        <v>3.2835087999999999</v>
+      </c>
+      <c r="I10">
+        <v>12</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0.5</v>
+      </c>
+      <c r="L10">
+        <v>0.5</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>36</v>
+      </c>
+      <c r="O10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>33972.815999999999</v>
+      </c>
+      <c r="B11">
+        <v>31325.258000000002</v>
+      </c>
+      <c r="C11">
+        <v>31830.370999999999</v>
+      </c>
+      <c r="D11">
+        <v>31795.305</v>
+      </c>
+      <c r="E11">
+        <v>32176.771000000001</v>
+      </c>
+      <c r="G11">
+        <v>2647.5585999999998</v>
+      </c>
+      <c r="H11">
+        <v>7.7931679999999997</v>
+      </c>
+      <c r="I11">
+        <v>12</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1.5</v>
+      </c>
+      <c r="L11">
+        <v>0.5</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>34282.656000000003</v>
+      </c>
+      <c r="B12">
+        <v>33085</v>
+      </c>
+      <c r="C12">
+        <v>33357.32</v>
+      </c>
+      <c r="D12">
+        <v>33523.656000000003</v>
+      </c>
+      <c r="E12">
+        <v>31402.416000000001</v>
+      </c>
+      <c r="G12">
+        <v>1197.6561999999999</v>
+      </c>
+      <c r="H12">
+        <v>3.4934753999999999</v>
+      </c>
+      <c r="I12">
+        <v>14</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>0.5</v>
+      </c>
+      <c r="L12">
+        <v>0.5</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>34332.582000000002</v>
+      </c>
+      <c r="B13">
+        <v>32751.99</v>
+      </c>
+      <c r="C13">
+        <v>33403.203000000001</v>
+      </c>
+      <c r="D13">
+        <v>33110.824000000001</v>
+      </c>
+      <c r="E13">
+        <v>32516.171999999999</v>
+      </c>
+      <c r="G13">
+        <v>1580.5917999999999</v>
+      </c>
+      <c r="H13">
+        <v>4.6037663999999996</v>
+      </c>
+      <c r="I13">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>1.5</v>
+      </c>
+      <c r="L13">
+        <v>0.5</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>34503.883000000002</v>
+      </c>
+      <c r="B14">
+        <v>33259.938000000002</v>
+      </c>
+      <c r="C14">
+        <v>33212.105000000003</v>
+      </c>
+      <c r="D14">
+        <v>33205.144999999997</v>
+      </c>
+      <c r="E14">
+        <v>33107.65</v>
+      </c>
+      <c r="G14">
+        <v>1243.9453000000001</v>
+      </c>
+      <c r="H14">
+        <v>3.6052327000000002</v>
+      </c>
+      <c r="I14">
+        <v>15</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <v>2.5</v>
+      </c>
+      <c r="L14">
+        <v>0.5</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>34503.9</v>
+      </c>
+      <c r="B15">
+        <v>33261.277000000002</v>
+      </c>
+      <c r="C15">
+        <v>33808.410000000003</v>
+      </c>
+      <c r="D15">
+        <v>33431.593999999997</v>
+      </c>
+      <c r="E15">
+        <v>32887.449999999997</v>
+      </c>
+      <c r="G15">
+        <v>1242.6211000000001</v>
+      </c>
+      <c r="H15">
+        <v>3.6013934999999999</v>
+      </c>
+      <c r="I15">
+        <v>15</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>1.5</v>
+      </c>
+      <c r="L15">
+        <v>0.5</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15" t="s">
+        <v>39</v>
+      </c>
+      <c r="O15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>34566.14</v>
+      </c>
+      <c r="B16">
+        <v>33304.050000000003</v>
+      </c>
+      <c r="C16">
+        <v>33279.745999999999</v>
+      </c>
+      <c r="D16">
+        <v>33218.366999999998</v>
+      </c>
+      <c r="E16">
+        <v>33008.008000000002</v>
+      </c>
+      <c r="G16">
+        <v>1262.0898</v>
+      </c>
+      <c r="H16">
+        <v>3.6512315000000002</v>
+      </c>
+      <c r="I16">
+        <v>16</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <v>2.5</v>
+      </c>
+      <c r="L16">
+        <v>0.5</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16" t="s">
+        <v>40</v>
+      </c>
+      <c r="O16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>34621.9</v>
+      </c>
+      <c r="B17">
+        <v>33650.65</v>
+      </c>
+      <c r="C17">
+        <v>32964.28</v>
+      </c>
+      <c r="D17">
+        <v>33439.663999999997</v>
+      </c>
+      <c r="E17">
+        <v>35158.06</v>
+      </c>
+      <c r="G17">
+        <v>971.25</v>
+      </c>
+      <c r="H17">
+        <v>2.8053054999999998</v>
+      </c>
+      <c r="I17">
+        <v>19</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0.5</v>
+      </c>
+      <c r="L17">
+        <v>0.5</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>41</v>
+      </c>
+      <c r="O17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>34660.58</v>
+      </c>
+      <c r="B18">
+        <v>33522.15</v>
+      </c>
+      <c r="C18">
+        <v>33808.199999999997</v>
+      </c>
+      <c r="D18">
+        <v>33568.644999999997</v>
+      </c>
+      <c r="E18">
+        <v>33051.707000000002</v>
+      </c>
+      <c r="G18">
+        <v>1138.4296999999999</v>
+      </c>
+      <c r="H18">
+        <v>3.2845086999999999</v>
+      </c>
+      <c r="I18">
+        <v>18</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>1.5</v>
+      </c>
+      <c r="L18">
+        <v>0.5</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
+      </c>
+      <c r="N18" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>34664.214999999997</v>
+      </c>
+      <c r="B19">
+        <v>33617.983999999997</v>
+      </c>
+      <c r="C19">
+        <v>32937.612999999998</v>
+      </c>
+      <c r="D19">
+        <v>33431.366999999998</v>
+      </c>
+      <c r="E19">
+        <v>35422.144999999997</v>
+      </c>
+      <c r="G19">
+        <v>1046.2304999999999</v>
+      </c>
+      <c r="H19">
+        <v>3.018186</v>
+      </c>
+      <c r="I19">
+        <v>20</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0.5</v>
+      </c>
+      <c r="L19">
+        <v>0.5</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>34696.866999999998</v>
+      </c>
+      <c r="B20">
+        <v>33508.137000000002</v>
+      </c>
+      <c r="C20">
+        <v>33750.684000000001</v>
+      </c>
+      <c r="D20">
+        <v>33547.480000000003</v>
+      </c>
+      <c r="E20">
+        <v>33049.516000000003</v>
+      </c>
+      <c r="G20">
+        <v>1188.7304999999999</v>
+      </c>
+      <c r="H20">
+        <v>3.4260457</v>
+      </c>
+      <c r="I20">
+        <v>19</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <v>1.5</v>
+      </c>
+      <c r="L20">
+        <v>0.5</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20" t="s">
+        <v>45</v>
+      </c>
+      <c r="O20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>34777.31</v>
+      </c>
+      <c r="B21">
+        <v>33348.847999999998</v>
+      </c>
+      <c r="C21">
+        <v>33630.311999999998</v>
+      </c>
+      <c r="D21">
+        <v>33426.491999999998</v>
+      </c>
+      <c r="E21">
+        <v>33256.75</v>
+      </c>
+      <c r="G21">
+        <v>1428.4609</v>
+      </c>
+      <c r="H21">
+        <v>4.1074510000000002</v>
+      </c>
+      <c r="I21">
+        <v>22</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>1.5</v>
+      </c>
+      <c r="L21">
+        <v>0.5</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21" t="s">
+        <v>46</v>
+      </c>
+      <c r="O21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>34814.847999999998</v>
+      </c>
+      <c r="B22">
+        <v>33330.550000000003</v>
+      </c>
+      <c r="C22">
+        <v>33918.61</v>
+      </c>
+      <c r="D22">
+        <v>33541.17</v>
+      </c>
+      <c r="E22">
+        <v>33696.89</v>
+      </c>
+      <c r="G22">
+        <v>1484.2969000000001</v>
+      </c>
+      <c r="H22">
+        <v>4.2634020000000001</v>
+      </c>
+      <c r="I22">
+        <v>24</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>2.5</v>
+      </c>
+      <c r="L22">
+        <v>0.5</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22" t="s">
+        <v>47</v>
+      </c>
+      <c r="O22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>34845.199999999997</v>
+      </c>
+      <c r="B23">
+        <v>33584.14</v>
+      </c>
+      <c r="C23">
+        <v>33147.980000000003</v>
+      </c>
+      <c r="D23">
+        <v>33417.51</v>
+      </c>
+      <c r="E23">
+        <v>36182.061999999998</v>
+      </c>
+      <c r="G23">
+        <v>1261.0586000000001</v>
+      </c>
+      <c r="H23">
+        <v>3.6190311999999998</v>
+      </c>
+      <c r="I23">
+        <v>28</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0.5</v>
+      </c>
+      <c r="L23">
+        <v>0.5</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>48</v>
+      </c>
+      <c r="O23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>34856.156000000003</v>
+      </c>
+      <c r="B24">
+        <v>33400.75</v>
+      </c>
+      <c r="C24">
+        <v>34235.24</v>
+      </c>
+      <c r="D24">
+        <v>33629.074000000001</v>
+      </c>
+      <c r="E24">
+        <v>33924.305</v>
+      </c>
+      <c r="G24">
+        <v>1455.4061999999999</v>
+      </c>
+      <c r="H24">
+        <v>4.1754639999999998</v>
+      </c>
+      <c r="I24">
+        <v>27</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>2.5</v>
+      </c>
+      <c r="L24">
+        <v>0.5</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24" t="s">
+        <v>49</v>
+      </c>
+      <c r="O24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>34932.695</v>
+      </c>
+      <c r="B25">
+        <v>33776.362999999998</v>
+      </c>
+      <c r="C25">
+        <v>34085.758000000002</v>
+      </c>
+      <c r="D25">
+        <v>33746.92</v>
+      </c>
+      <c r="E25">
+        <v>34205.18</v>
+      </c>
+      <c r="G25">
+        <v>1156.3320000000001</v>
+      </c>
+      <c r="H25">
+        <v>3.3101710999999998</v>
+      </c>
+      <c r="I25">
+        <v>38</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>1.5</v>
+      </c>
+      <c r="L25">
+        <v>0.5</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25" t="s">
+        <v>50</v>
+      </c>
+      <c r="O25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>34940.6</v>
+      </c>
+      <c r="B26">
+        <v>33458.83</v>
+      </c>
+      <c r="C26">
+        <v>33225.277000000002</v>
+      </c>
+      <c r="D26">
+        <v>34202.120000000003</v>
+      </c>
+      <c r="E26">
+        <v>35740.01</v>
+      </c>
+      <c r="G26">
+        <v>1481.7734</v>
+      </c>
+      <c r="H26">
+        <v>4.2408356999999999</v>
+      </c>
+      <c r="I26">
+        <v>42</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0.5</v>
+      </c>
+      <c r="L26">
+        <v>0.5</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>51</v>
+      </c>
+      <c r="O26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>34957.32</v>
+      </c>
+      <c r="B27">
+        <v>33900.17</v>
+      </c>
+      <c r="C27">
+        <v>35644.324000000001</v>
+      </c>
+      <c r="D27">
+        <v>33704.616999999998</v>
+      </c>
+      <c r="E27">
+        <v>34341.964999999997</v>
+      </c>
+      <c r="G27">
+        <v>1057.1484</v>
+      </c>
+      <c r="H27">
+        <v>3.0241117000000002</v>
+      </c>
+      <c r="I27">
+        <v>46</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27">
+        <v>2.5</v>
+      </c>
+      <c r="L27">
+        <v>0.5</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+      <c r="N27" t="s">
+        <v>52</v>
+      </c>
+      <c r="O27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56AA7832-422D-474D-9029-8C20BADED3EB}">
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="14.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3">
+        <v>11137</v>
+      </c>
+      <c r="C3">
+        <v>11393</v>
+      </c>
+      <c r="D3">
+        <v>11649</v>
+      </c>
+      <c r="E3">
+        <v>12161</v>
+      </c>
+      <c r="F3">
+        <v>12673</v>
+      </c>
+      <c r="G3">
+        <v>13441</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4">
+        <v>13201036</v>
+      </c>
+      <c r="C4">
+        <v>11253828</v>
+      </c>
+      <c r="D4">
+        <v>13610550</v>
+      </c>
+      <c r="E4">
+        <v>13425975</v>
+      </c>
+      <c r="F4">
+        <v>12028980</v>
+      </c>
+      <c r="G4">
+        <v>11097733</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5">
+        <v>3633.32299804687</v>
+      </c>
+      <c r="C5">
+        <v>3354.67260742187</v>
+      </c>
+      <c r="D5">
+        <v>3689.24780273437</v>
+      </c>
+      <c r="E5">
+        <v>3664.14721679687</v>
+      </c>
+      <c r="F5">
+        <v>3468.28198242187</v>
+      </c>
+      <c r="G5">
+        <v>3331.32592773437</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6">
+        <v>2027.59313964843</v>
+      </c>
+      <c r="C6">
+        <v>1811.14013671875</v>
+      </c>
+      <c r="D6">
+        <v>1909.16870117187</v>
+      </c>
+      <c r="E6">
+        <v>1794.17077636718</v>
+      </c>
+      <c r="F6">
+        <v>1790.70654296875</v>
+      </c>
+      <c r="G6">
+        <v>1625.9521484375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7">
+        <v>1243.9453125</v>
+      </c>
+      <c r="C7">
+        <v>981.265625</v>
+      </c>
+      <c r="D7">
+        <v>1196.78125</v>
+      </c>
+      <c r="E7">
+        <v>963.41796875</v>
+      </c>
+      <c r="F7">
+        <v>963.564453125</v>
+      </c>
+      <c r="G7">
+        <v>836.1875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8">
+        <v>0.30797845125198298</v>
+      </c>
+      <c r="C8">
+        <v>0.41005450487136802</v>
+      </c>
+      <c r="D8">
+        <v>0.28651100397109902</v>
+      </c>
+      <c r="E8">
+        <v>0.29618674516677801</v>
+      </c>
+      <c r="F8">
+        <v>0.36941963434219299</v>
+      </c>
+      <c r="G8">
+        <v>0.41823726892471302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9">
+        <v>9.1373691558837802</v>
+      </c>
+      <c r="C9">
+        <v>8.2787790298461896</v>
+      </c>
+      <c r="D9">
+        <v>8.9011106491088796</v>
+      </c>
+      <c r="E9">
+        <v>8.5853748321533203</v>
+      </c>
+      <c r="F9">
+        <v>8.3441534042358398</v>
+      </c>
+      <c r="G9">
+        <v>7.8002729415893501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10">
+        <v>16457.9375</v>
+      </c>
+      <c r="C10">
+        <v>15205.9658203125</v>
+      </c>
+      <c r="D10">
+        <v>16974.73828125</v>
+      </c>
+      <c r="E10">
+        <v>17083.44921875</v>
+      </c>
+      <c r="F10">
+        <v>15752.4248046875</v>
+      </c>
+      <c r="G10">
+        <v>15308.9736328125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15">
+        <v>11137</v>
+      </c>
+      <c r="C15">
+        <v>11393</v>
+      </c>
+      <c r="D15">
+        <v>11649</v>
+      </c>
+      <c r="E15">
+        <v>12161</v>
+      </c>
+      <c r="F15">
+        <v>12673</v>
+      </c>
+      <c r="G15">
+        <v>13441</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16">
+        <v>14496148</v>
+      </c>
+      <c r="C16">
+        <v>11400156</v>
+      </c>
+      <c r="D16">
+        <v>13634391</v>
+      </c>
+      <c r="E16">
+        <v>12839149</v>
+      </c>
+      <c r="F16">
+        <v>11130683</v>
+      </c>
+      <c r="G16">
+        <v>13261562</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17">
+        <v>3807.38061523437</v>
+      </c>
+      <c r="C17">
+        <v>3376.41162109375</v>
+      </c>
+      <c r="D17">
+        <v>3692.4775390625</v>
+      </c>
+      <c r="E17">
+        <v>3583.17578125</v>
+      </c>
+      <c r="F17">
+        <v>3336.26782226562</v>
+      </c>
+      <c r="G17">
+        <v>3641.64282226562</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18">
+        <v>2009.55029296875</v>
+      </c>
+      <c r="C18">
+        <v>1676.74780273437</v>
+      </c>
+      <c r="D18">
+        <v>2143.0400390625</v>
+      </c>
+      <c r="E18">
+        <v>1890.3515625</v>
+      </c>
+      <c r="F18">
+        <v>1769.06982421875</v>
+      </c>
+      <c r="G18">
+        <v>2040.40551757812</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19">
+        <v>1337.4453125</v>
+      </c>
+      <c r="C19">
+        <v>874.6484375</v>
+      </c>
+      <c r="D19">
+        <v>1559.04296875</v>
+      </c>
+      <c r="E19">
+        <v>940.62109375</v>
+      </c>
+      <c r="F19">
+        <v>928.71484375</v>
+      </c>
+      <c r="G19">
+        <v>1474.203125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20">
+        <v>0.24008631706237701</v>
+      </c>
+      <c r="C20">
+        <v>0.40238368511199901</v>
+      </c>
+      <c r="D20">
+        <v>0.28526115417480402</v>
+      </c>
+      <c r="E20">
+        <v>0.32694917917251498</v>
+      </c>
+      <c r="F20">
+        <v>0.41650998592376698</v>
+      </c>
+      <c r="G20">
+        <v>0.304805517196655</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21">
+        <v>9.3456325531005806</v>
+      </c>
+      <c r="C21">
+        <v>7.9325494766235298</v>
+      </c>
+      <c r="D21">
+        <v>9.4764165878295898</v>
+      </c>
+      <c r="E21">
+        <v>8.7273540496826101</v>
+      </c>
+      <c r="F21">
+        <v>8.1423807144165004</v>
+      </c>
+      <c r="G21">
+        <v>9.1808357238769496</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22">
+        <v>17731.03515625</v>
+      </c>
+      <c r="C22">
+        <v>15167.111328125</v>
+      </c>
+      <c r="D22">
+        <v>16619.369140625</v>
+      </c>
+      <c r="E22">
+        <v>16247.474609375</v>
+      </c>
+      <c r="F22">
+        <v>15043.916015625</v>
+      </c>
+      <c r="G22">
+        <v>16526.798828125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27">
+        <v>11137</v>
+      </c>
+      <c r="C27">
+        <v>11393</v>
+      </c>
+      <c r="D27">
+        <v>11649</v>
+      </c>
+      <c r="E27">
+        <v>12161</v>
+      </c>
+      <c r="F27">
+        <v>12673</v>
+      </c>
+      <c r="G27">
+        <v>13441</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28">
+        <v>20997686</v>
+      </c>
+      <c r="C28">
+        <v>20357744</v>
+      </c>
+      <c r="D28">
+        <v>16972888</v>
+      </c>
+      <c r="E28">
+        <v>18383196</v>
+      </c>
+      <c r="F28" s="4">
+        <v>4.0000000801635002E+20</v>
+      </c>
+      <c r="G28">
+        <v>20352586</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29">
+        <v>4582.3232421875</v>
+      </c>
+      <c r="C29">
+        <v>4511.95556640625</v>
+      </c>
+      <c r="D29">
+        <v>4119.81640625</v>
+      </c>
+      <c r="E29">
+        <v>4287.56298828125</v>
+      </c>
+      <c r="F29">
+        <v>20000000000</v>
+      </c>
+      <c r="G29">
+        <v>4511.38427734375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30">
+        <v>1598.52185058593</v>
+      </c>
+      <c r="C30">
+        <v>1598.38427734375</v>
+      </c>
+      <c r="D30">
+        <v>1468.82458496093</v>
+      </c>
+      <c r="E30">
+        <v>1429.82641601562</v>
+      </c>
+      <c r="F30">
+        <v>4000001024</v>
+      </c>
+      <c r="G30">
+        <v>1566.6474609375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31">
+        <v>99.00390625</v>
+      </c>
+      <c r="C31">
+        <v>128.67578125</v>
+      </c>
+      <c r="D31">
+        <v>123.16796875</v>
+      </c>
+      <c r="E31">
+        <v>66.74609375</v>
+      </c>
+      <c r="F31">
+        <v>62.05078125</v>
+      </c>
+      <c r="G31">
+        <v>138.578125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32">
+        <v>-0.100734829902648</v>
+      </c>
+      <c r="C32">
+        <v>-6.7188024520873996E-2</v>
+      </c>
+      <c r="D32">
+        <v>0.110252022743225</v>
+      </c>
+      <c r="E32">
+        <v>3.63211631774902E-2</v>
+      </c>
+      <c r="F32">
+        <v>-20968688844800</v>
+      </c>
+      <c r="G32">
+        <v>-6.6917657852172796E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33">
+        <v>9.00884914398193</v>
+      </c>
+      <c r="C33">
+        <v>8.9274435043334908</v>
+      </c>
+      <c r="D33">
+        <v>8.1759958267211896</v>
+      </c>
+      <c r="E33">
+        <v>8.2598686218261701</v>
+      </c>
+      <c r="F33">
+        <v>13064511</v>
+      </c>
+      <c r="G33">
+        <v>8.8551073074340803</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34">
+        <v>21500.744140625</v>
+      </c>
+      <c r="C34">
+        <v>21045.197265625</v>
+      </c>
+      <c r="D34">
+        <v>19192.361328125</v>
+      </c>
+      <c r="E34">
+        <v>20329.900390625</v>
+      </c>
+      <c r="F34">
+        <v>99999997952</v>
+      </c>
+      <c r="G34">
+        <v>21227.021484375</v>
       </c>
     </row>
   </sheetData>

--- a/saved_models/results.xlsx
+++ b/saved_models/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharmProjects\AtomEnergyLevels\saved_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC354A9-FB50-467F-BFBE-14D82775DC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8754FB15-EAC8-4B46-BEFA-ABCB3771466E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="13763" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="13763" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="K" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="71">
   <si>
     <t>Mean Squared Error (MSE)</t>
   </si>
@@ -233,7 +233,13 @@
     <t>binded, no weights</t>
   </si>
   <si>
-    <t>inversed binded, no weights</t>
+    <t>log binded, no weights</t>
+  </si>
+  <si>
+    <t>inversed raw, no weights</t>
+  </si>
+  <si>
+    <t>inversed binded (with clipping), no weights</t>
   </si>
 </sst>
 </file>
@@ -602,15 +608,6 @@
       <c r="B2">
         <v>13201036</v>
       </c>
-      <c r="C2">
-        <v>13201036</v>
-      </c>
-      <c r="D2">
-        <v>13201036</v>
-      </c>
-      <c r="E2">
-        <v>13201036</v>
-      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
@@ -619,15 +616,6 @@
       <c r="B3">
         <v>3633.32299804687</v>
       </c>
-      <c r="C3">
-        <v>3633.32299804687</v>
-      </c>
-      <c r="D3">
-        <v>3633.32299804687</v>
-      </c>
-      <c r="E3">
-        <v>3633.32299804687</v>
-      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
@@ -635,15 +623,6 @@
       </c>
       <c r="B4">
         <v>2027.59313964843</v>
-      </c>
-      <c r="C4">
-        <v>2027.59313964843</v>
-      </c>
-      <c r="D4">
-        <v>2027.59313964843</v>
-      </c>
-      <c r="E4">
-        <v>2027.59326171875</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
@@ -653,15 +632,6 @@
       <c r="B5">
         <v>1243.9453125</v>
       </c>
-      <c r="C5">
-        <v>1243.9453125</v>
-      </c>
-      <c r="D5">
-        <v>1243.9453125</v>
-      </c>
-      <c r="E5">
-        <v>1243.9453125</v>
-      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
@@ -670,15 +640,6 @@
       <c r="B6">
         <v>0.30797845125198298</v>
       </c>
-      <c r="C6">
-        <v>0.30797845125198298</v>
-      </c>
-      <c r="D6">
-        <v>0.30797845125198298</v>
-      </c>
-      <c r="E6">
-        <v>0.30797845125198298</v>
-      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
@@ -687,15 +648,6 @@
       <c r="B7">
         <v>9.1373691558837802</v>
       </c>
-      <c r="C7">
-        <v>9.1373691558837802</v>
-      </c>
-      <c r="D7">
-        <v>9.1373691558837802</v>
-      </c>
-      <c r="E7">
-        <v>9.1373691558837802</v>
-      </c>
       <c r="G7" s="1"/>
       <c r="I7" s="1"/>
     </row>
@@ -704,15 +656,6 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>16457.9375</v>
-      </c>
-      <c r="C8">
-        <v>16457.9375</v>
-      </c>
-      <c r="D8">
-        <v>16457.9375</v>
-      </c>
-      <c r="E8">
         <v>16457.9375</v>
       </c>
     </row>
@@ -2045,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56AA7832-422D-474D-9029-8C20BADED3EB}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.3984375" bestFit="1" customWidth="1"/>
@@ -2477,7 +2420,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -2530,161 +2473,459 @@
       <c r="A28" t="s">
         <v>59</v>
       </c>
-      <c r="B28">
-        <v>20997686</v>
-      </c>
-      <c r="C28">
-        <v>20357744</v>
-      </c>
-      <c r="D28">
-        <v>16972888</v>
-      </c>
-      <c r="E28">
-        <v>18383196</v>
-      </c>
-      <c r="F28" s="4">
-        <v>4.0000000801635002E+20</v>
-      </c>
-      <c r="G28">
-        <v>20352586</v>
-      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>60</v>
       </c>
-      <c r="B29">
-        <v>4582.3232421875</v>
-      </c>
-      <c r="C29">
-        <v>4511.95556640625</v>
-      </c>
-      <c r="D29">
-        <v>4119.81640625</v>
-      </c>
-      <c r="E29">
-        <v>4287.56298828125</v>
-      </c>
-      <c r="F29">
-        <v>20000000000</v>
-      </c>
-      <c r="G29">
-        <v>4511.38427734375</v>
-      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>61</v>
       </c>
-      <c r="B30">
-        <v>1598.52185058593</v>
-      </c>
-      <c r="C30">
-        <v>1598.38427734375</v>
-      </c>
-      <c r="D30">
-        <v>1468.82458496093</v>
-      </c>
-      <c r="E30">
-        <v>1429.82641601562</v>
-      </c>
-      <c r="F30">
-        <v>4000001024</v>
-      </c>
-      <c r="G30">
-        <v>1566.6474609375</v>
-      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>62</v>
       </c>
-      <c r="B31">
-        <v>99.00390625</v>
-      </c>
-      <c r="C31">
-        <v>128.67578125</v>
-      </c>
-      <c r="D31">
-        <v>123.16796875</v>
-      </c>
-      <c r="E31">
-        <v>66.74609375</v>
-      </c>
-      <c r="F31">
-        <v>62.05078125</v>
-      </c>
-      <c r="G31">
-        <v>138.578125</v>
-      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>63</v>
       </c>
-      <c r="B32">
-        <v>-0.100734829902648</v>
-      </c>
-      <c r="C32">
-        <v>-6.7188024520873996E-2</v>
-      </c>
-      <c r="D32">
-        <v>0.110252022743225</v>
-      </c>
-      <c r="E32">
-        <v>3.63211631774902E-2</v>
-      </c>
-      <c r="F32">
-        <v>-20968688844800</v>
-      </c>
-      <c r="G32">
-        <v>-6.6917657852172796E-2</v>
-      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>64</v>
       </c>
-      <c r="B33">
-        <v>9.00884914398193</v>
-      </c>
-      <c r="C33">
-        <v>8.9274435043334908</v>
-      </c>
-      <c r="D33">
-        <v>8.1759958267211896</v>
-      </c>
-      <c r="E33">
-        <v>8.2598686218261701</v>
-      </c>
-      <c r="F33">
-        <v>13064511</v>
-      </c>
-      <c r="G33">
-        <v>8.8551073074340803</v>
-      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>65</v>
       </c>
-      <c r="B34">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38">
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39">
+        <v>11137</v>
+      </c>
+      <c r="C39">
+        <v>11393</v>
+      </c>
+      <c r="D39">
+        <v>11649</v>
+      </c>
+      <c r="E39">
+        <v>12161</v>
+      </c>
+      <c r="F39">
+        <v>12673</v>
+      </c>
+      <c r="G39">
+        <v>13441</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40">
+        <v>20997686</v>
+      </c>
+      <c r="C40">
+        <v>20357744</v>
+      </c>
+      <c r="D40">
+        <v>16972888</v>
+      </c>
+      <c r="E40">
+        <v>18383196</v>
+      </c>
+      <c r="F40" s="4">
+        <v>4.0000000801635002E+20</v>
+      </c>
+      <c r="G40">
+        <v>20352586</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41">
+        <v>4582.3232421875</v>
+      </c>
+      <c r="C41">
+        <v>4511.95556640625</v>
+      </c>
+      <c r="D41">
+        <v>4119.81640625</v>
+      </c>
+      <c r="E41">
+        <v>4287.56298828125</v>
+      </c>
+      <c r="F41">
+        <v>20000000000</v>
+      </c>
+      <c r="G41">
+        <v>4511.38427734375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42">
+        <v>1598.52185058593</v>
+      </c>
+      <c r="C42">
+        <v>1598.38427734375</v>
+      </c>
+      <c r="D42">
+        <v>1468.82458496093</v>
+      </c>
+      <c r="E42">
+        <v>1429.82641601562</v>
+      </c>
+      <c r="F42">
+        <v>4000001024</v>
+      </c>
+      <c r="G42">
+        <v>1566.6474609375</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43">
+        <v>99.00390625</v>
+      </c>
+      <c r="C43">
+        <v>128.67578125</v>
+      </c>
+      <c r="D43">
+        <v>123.16796875</v>
+      </c>
+      <c r="E43">
+        <v>66.74609375</v>
+      </c>
+      <c r="F43">
+        <v>62.05078125</v>
+      </c>
+      <c r="G43">
+        <v>138.578125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44">
+        <v>-0.100734829902648</v>
+      </c>
+      <c r="C44">
+        <v>-6.7188024520873996E-2</v>
+      </c>
+      <c r="D44">
+        <v>0.110252022743225</v>
+      </c>
+      <c r="E44">
+        <v>3.63211631774902E-2</v>
+      </c>
+      <c r="F44">
+        <v>-20968688844800</v>
+      </c>
+      <c r="G44">
+        <v>-6.6917657852172796E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45">
+        <v>9.00884914398193</v>
+      </c>
+      <c r="C45">
+        <v>8.9274435043334908</v>
+      </c>
+      <c r="D45">
+        <v>8.1759958267211896</v>
+      </c>
+      <c r="E45">
+        <v>8.2598686218261701</v>
+      </c>
+      <c r="F45">
+        <v>13064511</v>
+      </c>
+      <c r="G45">
+        <v>8.8551073074340803</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46">
         <v>21500.744140625</v>
       </c>
-      <c r="C34">
+      <c r="C46">
         <v>21045.197265625</v>
       </c>
-      <c r="D34">
+      <c r="D46">
         <v>19192.361328125</v>
       </c>
-      <c r="E34">
+      <c r="E46">
         <v>20329.900390625</v>
       </c>
-      <c r="F34">
+      <c r="F46">
         <v>99999997952</v>
       </c>
-      <c r="G34">
+      <c r="G46">
         <v>21227.021484375</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>7</v>
+      </c>
+      <c r="G50">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51">
+        <v>11137</v>
+      </c>
+      <c r="C51">
+        <v>11393</v>
+      </c>
+      <c r="D51">
+        <v>11649</v>
+      </c>
+      <c r="E51">
+        <v>12161</v>
+      </c>
+      <c r="F51">
+        <v>12673</v>
+      </c>
+      <c r="G51">
+        <v>13441</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52">
+        <v>16448689</v>
+      </c>
+      <c r="C52">
+        <v>12672312</v>
+      </c>
+      <c r="D52">
+        <v>12114899</v>
+      </c>
+      <c r="E52">
+        <v>11117850</v>
+      </c>
+      <c r="F52">
+        <v>11424037</v>
+      </c>
+      <c r="G52">
+        <v>12324045</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53">
+        <v>4055.6982421875</v>
+      </c>
+      <c r="C53">
+        <v>3559.81909179687</v>
+      </c>
+      <c r="D53">
+        <v>3480.64624023437</v>
+      </c>
+      <c r="E53">
+        <v>3334.34399414062</v>
+      </c>
+      <c r="F53">
+        <v>3379.9462890625</v>
+      </c>
+      <c r="G53">
+        <v>3510.56201171875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54">
+        <v>1314.94775390625</v>
+      </c>
+      <c r="C54">
+        <v>1083.91198730468</v>
+      </c>
+      <c r="D54">
+        <v>1063.09594726562</v>
+      </c>
+      <c r="E54">
+        <v>1005.49749755859</v>
+      </c>
+      <c r="F54">
+        <v>1029.32458496093</v>
+      </c>
+      <c r="G54">
+        <v>1072.7138671875</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55">
+        <v>206.48046875</v>
+      </c>
+      <c r="C55">
+        <v>137.33984375</v>
+      </c>
+      <c r="D55">
+        <v>109.01171875</v>
+      </c>
+      <c r="E55">
+        <v>101.171875</v>
+      </c>
+      <c r="F55">
+        <v>119.4453125</v>
+      </c>
+      <c r="G55">
+        <v>127.51953125</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56">
+        <v>0.137731432914733</v>
+      </c>
+      <c r="C56">
+        <v>0.33569556474685602</v>
+      </c>
+      <c r="D56">
+        <v>0.36491608619689903</v>
+      </c>
+      <c r="E56">
+        <v>0.41718316078186002</v>
+      </c>
+      <c r="F56">
+        <v>0.40113228559494002</v>
+      </c>
+      <c r="G56">
+        <v>0.35395234823226901</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57">
+        <v>7.7218508720397896</v>
+      </c>
+      <c r="C57">
+        <v>6.5894818305969203</v>
+      </c>
+      <c r="D57">
+        <v>6.4378457069396902</v>
+      </c>
+      <c r="E57">
+        <v>6.1210474967956499</v>
+      </c>
+      <c r="F57">
+        <v>6.2541313171386701</v>
+      </c>
+      <c r="G57">
+        <v>6.5000338554382298</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58">
+        <v>19503.509765625</v>
+      </c>
+      <c r="C58">
+        <v>17312.58984375</v>
+      </c>
+      <c r="D58">
+        <v>16905.634765625</v>
+      </c>
+      <c r="E58">
+        <v>16195.60546875</v>
+      </c>
+      <c r="F58">
+        <v>16387.603515625</v>
+      </c>
+      <c r="G58">
+        <v>17043.69140625</v>
       </c>
     </row>
   </sheetData>
